--- a/results/qwen3_5_9b/comparison_ToTRAG/ToTRAG_evaluated.xlsx
+++ b/results/qwen3_5_9b/comparison_ToTRAG/ToTRAG_evaluated.xlsx
@@ -505,35 +505,37 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.01010100960871342</v>
+        <v>0.2039800945104083</v>
       </c>
       <c r="D2" t="n">
-        <v>7.188271943170174e-260</v>
+        <v>0.02708196379994952</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3365101218223572</v>
+        <v>0.609032928943634</v>
       </c>
       <c r="F2" t="n">
-        <v>12.42500000000001</v>
+        <v>28.63575203252034</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06717123935666983</v>
+        <v>1.192999053926206</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
       <c r="K2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.1875</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4904458598726115</v>
       </c>
     </row>
     <row r="3">
@@ -546,35 +548,37 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.1212121186409551</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>8.588198359462805e-232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3989461362361908</v>
+        <v>0.4616523385047913</v>
       </c>
       <c r="F3" t="n">
-        <v>12.42500000000001</v>
+        <v>55.13444444444445</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6513761467889908</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.3260869565217391</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2424242424242424</v>
       </c>
     </row>
     <row r="4">
@@ -587,35 +591,37 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.2633744809998477</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1.063648948210143e-155</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2873830199241638</v>
+        <v>0.5487219095230103</v>
       </c>
       <c r="F4" t="n">
-        <v>12.42500000000001</v>
+        <v>44.09318075117372</v>
       </c>
       <c r="G4" t="n">
-        <v>0.07585470085470085</v>
+        <v>0.5587606837606838</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.273972602739726</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2248062015503876</v>
       </c>
     </row>
     <row r="5">
@@ -628,35 +634,37 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.1428571393696429</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>8.856439368561365e-156</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2863562107086182</v>
+        <v>0.5586528778076172</v>
       </c>
       <c r="F5" t="n">
-        <v>12.42500000000001</v>
+        <v>45.30535353535356</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05810147299509002</v>
+        <v>0.3731587561374796</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3577981651376147</v>
       </c>
     </row>
     <row r="6">
@@ -669,35 +677,37 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01273885288652687</v>
+        <v>0.1855670069167819</v>
       </c>
       <c r="D6" t="n">
-        <v>7.842246496009318e-255</v>
+        <v>0.01028895573512684</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3232610821723938</v>
+        <v>0.6066243648529053</v>
       </c>
       <c r="F6" t="n">
-        <v>12.42500000000001</v>
+        <v>47.53497975708504</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08160919540229886</v>
+        <v>0.4011494252873563</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.3823529411764706</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2783505154639175</v>
       </c>
     </row>
     <row r="7">
@@ -710,35 +720,37 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.004032257864935623</v>
+        <v>0.2313829741911287</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.01304333068301503</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3543217778205872</v>
+        <v>0.6347999572753906</v>
       </c>
       <c r="F7" t="n">
-        <v>12.42500000000001</v>
+        <v>24.27093305763765</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02065755018911842</v>
+        <v>0.5216758801280186</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
       <c r="K7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.715099715099715</v>
       </c>
     </row>
     <row r="8">
@@ -751,35 +763,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.306306301988475</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.05078293018565865</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3380750119686127</v>
+        <v>0.6161172986030579</v>
       </c>
       <c r="F8" t="n">
-        <v>12.42500000000001</v>
+        <v>53.59483530961793</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04930555555555555</v>
+        <v>0.4916666666666666</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
       <c r="K8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -792,35 +806,37 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.006993006649469429</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>4.626996437597695e-283</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3232589066028595</v>
+        <v>0.4887156784534454</v>
       </c>
       <c r="F9" t="n">
-        <v>12.42500000000001</v>
+        <v>-66.63173913043474</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04113557358053303</v>
+        <v>0.1060254924681344</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.6875</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.1176470588235294</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.06666666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -833,35 +849,37 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.2394957933194161</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.04772374788633845</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3234608471393585</v>
+        <v>0.6305142641067505</v>
       </c>
       <c r="F10" t="n">
-        <v>12.42500000000001</v>
+        <v>25.51861921080783</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04695767195767196</v>
+        <v>0.9907407407407407</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.2576687116564417</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.4961240310077519</v>
       </c>
     </row>
     <row r="11">
@@ -874,35 +892,37 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.006756756424625656</v>
+        <v>0.1705426319283698</v>
       </c>
       <c r="D11" t="n">
-        <v>3.199290466293744e-295</v>
+        <v>3.40454083265753e-156</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3082520365715027</v>
+        <v>0.5401231646537781</v>
       </c>
       <c r="F11" t="n">
-        <v>12.42500000000001</v>
+        <v>40.02442073170732</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03881902679059596</v>
+        <v>0.2914160743575724</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.3972602739726027</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3406593406593407</v>
       </c>
     </row>
     <row r="12">
@@ -915,35 +935,37 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.2260273922673697</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.05641986736762369</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3188543021678925</v>
+        <v>0.625409722328186</v>
       </c>
       <c r="F12" t="n">
-        <v>12.42500000000001</v>
+        <v>19.75291345278771</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04043280182232346</v>
+        <v>1.050113895216401</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
       <c r="K12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.2295918367346939</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.5289855072463768</v>
       </c>
     </row>
     <row r="13">
@@ -956,19 +978,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.006644517945718055</v>
+        <v>0.03947368369806094</v>
       </c>
       <c r="D13" t="n">
-        <v>1.737745674680046e-291</v>
+        <v>4.683989219383579e-192</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3241649270057678</v>
+        <v>0.4514622688293457</v>
       </c>
       <c r="F13" t="n">
-        <v>12.42500000000001</v>
+        <v>44.15000000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0393569844789357</v>
+        <v>0.05432372505543237</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -976,15 +998,17 @@
       <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
       <c r="K13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="14">
@@ -997,35 +1021,37 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.2182468644167166</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.04452889295323417</v>
       </c>
       <c r="E14" t="n">
-        <v>0.321511834859848</v>
+        <v>0.6200010776519775</v>
       </c>
       <c r="F14" t="n">
-        <v>12.42500000000001</v>
+        <v>21.4584013470367</v>
       </c>
       <c r="G14" t="n">
-        <v>0.03944444444444444</v>
+        <v>0.9322222222222222</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
       <c r="K14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.2275132275132275</v>
       </c>
       <c r="M14" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.4980694980694981</v>
       </c>
     </row>
     <row r="15">
@@ -1038,35 +1064,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.1944444402006174</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>0.02626033991055504</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3408587276935577</v>
+        <v>0.6527310013771057</v>
       </c>
       <c r="F15" t="n">
-        <v>12.42500000000001</v>
+        <v>60.59182352941181</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.6559356136820925</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
       <c r="K15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M15" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1946308724832215</v>
       </c>
     </row>
     <row r="16">
@@ -1079,35 +1107,37 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.2127659531399956</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1.286605803856702e-155</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3275765478610992</v>
+        <v>0.6298616528511047</v>
       </c>
       <c r="F16" t="n">
-        <v>12.42500000000001</v>
+        <v>45.03285714285718</v>
       </c>
       <c r="G16" t="n">
-        <v>0.101283880171184</v>
+        <v>0.609129814550642</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
       <c r="K16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2356687898089172</v>
       </c>
     </row>
     <row r="17">
@@ -1120,35 +1150,37 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.1853658491612137</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>7.084523236700412e-79</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3282608687877655</v>
+        <v>0.6372036337852478</v>
       </c>
       <c r="F17" t="n">
-        <v>12.42500000000001</v>
+        <v>80.65315527190069</v>
       </c>
       <c r="G17" t="n">
-        <v>0.09543010752688172</v>
+        <v>0.6881720430107527</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
       <c r="K17" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="M17" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.3478260869565217</v>
       </c>
     </row>
     <row r="18">
@@ -1161,35 +1193,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.2383612624394439</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.02161718968462057</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3524843156337738</v>
+        <v>0.6430540084838867</v>
       </c>
       <c r="F18" t="n">
-        <v>12.42500000000001</v>
+        <v>44.14400566739977</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02764797507788162</v>
+        <v>0.3668224299065421</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
       <c r="K18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.2090909090909091</v>
       </c>
       <c r="M18" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.4886363636363636</v>
       </c>
     </row>
     <row r="19">
@@ -1202,35 +1236,37 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.136752132536262</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>3.91211651022209e-156</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3208551406860352</v>
+        <v>0.6244118809700012</v>
       </c>
       <c r="F19" t="n">
-        <v>12.42500000000001</v>
+        <v>8.833696900114802</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04680290046143705</v>
+        <v>0.5003295978905735</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.2533333333333334</v>
       </c>
       <c r="M19" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.2737430167597765</v>
       </c>
     </row>
     <row r="20">
@@ -1243,35 +1279,37 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.008032128120514206</v>
+        <v>0.2172948952553823</v>
       </c>
       <c r="D20" t="n">
-        <v>1.21304235279905e-268</v>
+        <v>0.02298274698020877</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3401677906513214</v>
+        <v>0.6453647017478943</v>
       </c>
       <c r="F20" t="n">
-        <v>12.42500000000001</v>
+        <v>40.17219993817142</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05039034776437189</v>
+        <v>1.014904187366927</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.2516556291390729</v>
       </c>
       <c r="M20" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.4795539033457249</v>
       </c>
     </row>
     <row r="21">
@@ -1284,35 +1322,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.1575757528137743</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>6.505216587075523e-79</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3378615379333496</v>
+        <v>0.5629197359085083</v>
       </c>
       <c r="F21" t="n">
-        <v>12.42500000000001</v>
+        <v>27.64402332875216</v>
       </c>
       <c r="G21" t="n">
-        <v>0.04022662889518414</v>
+        <v>1.756373937677054</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
       <c r="K21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.1318327974276527</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0136986301369863</v>
+        <v>0.4576719576719577</v>
       </c>
     </row>
     <row r="22">
@@ -1325,35 +1365,37 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.252427181581676</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.004639200749766557</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3471125662326813</v>
+        <v>0.6102253198623657</v>
       </c>
       <c r="F22" t="n">
-        <v>12.42500000000001</v>
+        <v>55.60000000000002</v>
       </c>
       <c r="G22" t="n">
-        <v>0.04303030303030303</v>
+        <v>0.2272727272727273</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
       <c r="K22" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.3043478260869565</v>
       </c>
       <c r="M22" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.1428571428571428</v>
       </c>
     </row>
     <row r="23">
@@ -1366,35 +1408,37 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.005847952928251443</v>
+        <v>0.29999999560552</v>
       </c>
       <c r="D23" t="n">
-        <v>1.811128572821972e-307</v>
+        <v>0.01997567096383857</v>
       </c>
       <c r="E23" t="n">
-        <v>0.351656973361969</v>
+        <v>0.6520578265190125</v>
       </c>
       <c r="F23" t="n">
-        <v>12.42500000000001</v>
+        <v>39.53967503361724</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03261368856224162</v>
+        <v>0.5043638033991732</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" t="n">
         <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>0.1712328767123288</v>
       </c>
       <c r="M23" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.5620437956204379</v>
       </c>
     </row>
     <row r="24">
@@ -1407,35 +1451,37 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.119658117682811</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>3.477033749486991e-159</v>
       </c>
       <c r="E24" t="n">
-        <v>0.31206414103508</v>
+        <v>0.4788866937160492</v>
       </c>
       <c r="F24" t="n">
-        <v>12.42500000000001</v>
+        <v>-9.401666666666671</v>
       </c>
       <c r="G24" t="n">
-        <v>0.109062980030722</v>
+        <v>0.2089093701996928</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M24" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1071428571428571</v>
       </c>
     </row>
     <row r="25">
@@ -1448,35 +1494,37 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.2352941137852963</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>5.470936099096101e-156</v>
       </c>
       <c r="E25" t="n">
-        <v>0.328554779291153</v>
+        <v>0.5007578134536743</v>
       </c>
       <c r="F25" t="n">
-        <v>12.42500000000001</v>
+        <v>41.37414285714289</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1070889894419306</v>
+        <v>0.3996983408748115</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.303030303030303</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1764705882352941</v>
       </c>
     </row>
     <row r="26">
@@ -1489,35 +1537,37 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.3076923027695109</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.05478905986373354</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3231311142444611</v>
+        <v>0.6521477103233337</v>
       </c>
       <c r="F26" t="n">
-        <v>12.42500000000001</v>
+        <v>52.43493877551023</v>
       </c>
       <c r="G26" t="n">
-        <v>0.123050259965338</v>
+        <v>0.9150779896013865</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
       <c r="K26" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="27">
@@ -1530,35 +1580,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.1419354809107181</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>8.499834710984666e-157</v>
       </c>
       <c r="E27" t="n">
-        <v>0.311333566904068</v>
+        <v>0.4949567317962646</v>
       </c>
       <c r="F27" t="n">
-        <v>12.42500000000001</v>
+        <v>42.73338461538464</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09712722298221614</v>
+        <v>0.2859097127222982</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -1571,35 +1623,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.1830065320859499</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>2.340689708356918e-156</v>
       </c>
       <c r="E28" t="n">
-        <v>0.327028751373291</v>
+        <v>0.6263670325279236</v>
       </c>
       <c r="F28" t="n">
-        <v>12.42500000000001</v>
+        <v>72.27833333333334</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1075757575757576</v>
+        <v>0.3757575757575757</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
       <c r="K28" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.5161290322580645</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1463414634146341</v>
       </c>
     </row>
     <row r="29">
@@ -1612,35 +1666,37 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.1261261236587939</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>3.522566183220564e-235</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3222382366657257</v>
+        <v>0.472301185131073</v>
       </c>
       <c r="F29" t="n">
-        <v>12.42500000000001</v>
+        <v>8.045000000000016</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1232638888888889</v>
+        <v>0.2899305555555556</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1358024691358025</v>
       </c>
     </row>
     <row r="30">
@@ -1653,35 +1709,37 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.05714285490204091</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4336258769035339</v>
+        <v>0.5066623687744141</v>
       </c>
       <c r="F30" t="n">
-        <v>12.42500000000001</v>
+        <v>25.37625000000003</v>
       </c>
       <c r="G30" t="n">
-        <v>0.71</v>
+        <v>4.4</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="M30" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2682926829268293</v>
       </c>
     </row>
     <row r="31">
@@ -1694,35 +1752,37 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.1052631552354571</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>2.659276018264461e-155</v>
       </c>
       <c r="E31" t="n">
-        <v>0.415562242269516</v>
+        <v>0.5415123105049133</v>
       </c>
       <c r="F31" t="n">
-        <v>12.42500000000001</v>
+        <v>19.74704545454546</v>
       </c>
       <c r="G31" t="n">
-        <v>0.6893203883495146</v>
+        <v>3.41747572815534</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
       <c r="K31" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="M31" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1836734693877551</v>
       </c>
     </row>
     <row r="32">
@@ -1735,35 +1795,37 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.1298701278057008</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1.884690172697143e-155</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4121761322021484</v>
+        <v>0.5178974866867065</v>
       </c>
       <c r="F32" t="n">
-        <v>12.42500000000001</v>
+        <v>30.91062500000001</v>
       </c>
       <c r="G32" t="n">
-        <v>0.71</v>
+        <v>4.73</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
       <c r="K32" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>0.3818181818181818</v>
       </c>
       <c r="M32" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.3055555555555556</v>
       </c>
     </row>
     <row r="33">
@@ -1776,35 +1838,37 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.1944444397926313</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>2.733132671560163e-155</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3997314274311066</v>
+        <v>0.5764088034629822</v>
       </c>
       <c r="F33" t="n">
-        <v>12.42500000000001</v>
+        <v>27.63911342894394</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1966759002770083</v>
+        <v>1.78393351800554</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
       <c r="K33" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>0.2428571428571429</v>
       </c>
       <c r="M33" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2941176470588235</v>
       </c>
     </row>
     <row r="34">
@@ -1817,35 +1881,37 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.2222222172263714</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>3.767803189669989e-155</v>
       </c>
       <c r="E34" t="n">
-        <v>0.3917847871780396</v>
+        <v>0.5870185494422913</v>
       </c>
       <c r="F34" t="n">
-        <v>12.42500000000001</v>
+        <v>66.32692978923347</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1031976744186047</v>
+        <v>1.082848837209302</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
       <c r="K34" t="n">
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>0.2844036697247707</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2941176470588235</v>
       </c>
     </row>
     <row r="35">
@@ -1858,35 +1924,37 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.2098360610386456</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>2.479793130855319e-155</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3391465246677399</v>
+        <v>0.6394355893135071</v>
       </c>
       <c r="F35" t="n">
-        <v>12.42500000000001</v>
+        <v>24.34178211009177</v>
       </c>
       <c r="G35" t="n">
-        <v>0.06217162872154115</v>
+        <v>0.6322241681260946</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
       <c r="K35" t="n">
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="M35" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4366197183098592</v>
       </c>
     </row>
     <row r="36">
@@ -1899,35 +1967,37 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.2539682493043308</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.08317032070326827</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3042621910572052</v>
+        <v>0.7270490527153015</v>
       </c>
       <c r="F36" t="n">
-        <v>12.42500000000001</v>
+        <v>36.73173076923078</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1125198098256735</v>
+        <v>0.873217115689382</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
       <c r="K36" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>0.3090909090909091</v>
       </c>
       <c r="M36" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="37">
@@ -1940,35 +2010,37 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.2312499950031251</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>0.01714255775906496</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3632136583328247</v>
+        <v>0.6504281163215637</v>
       </c>
       <c r="F37" t="n">
-        <v>12.42500000000001</v>
+        <v>66.73094924812031</v>
       </c>
       <c r="G37" t="n">
-        <v>0.07529162248144221</v>
+        <v>1.034994697773065</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
       <c r="K37" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.5187165775401069</v>
       </c>
     </row>
     <row r="38">
@@ -1981,35 +2053,37 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.3021582684126081</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>0.01959763823273189</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3629776239395142</v>
+        <v>0.6193524599075317</v>
       </c>
       <c r="F38" t="n">
-        <v>12.42500000000001</v>
+        <v>46.82653953356089</v>
       </c>
       <c r="G38" t="n">
-        <v>0.09184993531694696</v>
+        <v>1.206985769728331</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="M38" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.5979899497487438</v>
       </c>
     </row>
     <row r="39">
@@ -2022,35 +2096,37 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.2048192726375382</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>0.02770717339510129</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3317360877990723</v>
+        <v>0.6224873661994934</v>
       </c>
       <c r="F39" t="n">
-        <v>12.42500000000001</v>
+        <v>29.17815934065936</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1047197640117994</v>
+        <v>0.6017699115044248</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>0.2954545454545455</v>
       </c>
       <c r="M39" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.2718446601941747</v>
       </c>
     </row>
     <row r="40">
@@ -2063,35 +2139,37 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.2419354791636317</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>3.893671983931577e-79</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2874237596988678</v>
+        <v>0.5179367065429688</v>
       </c>
       <c r="F40" t="n">
-        <v>12.42500000000001</v>
+        <v>55.77742351398604</v>
       </c>
       <c r="G40" t="n">
-        <v>0.07819383259911894</v>
+        <v>0.5980176211453745</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
       <c r="K40" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>0.275</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.393939393939394</v>
       </c>
     </row>
     <row r="41">
@@ -2104,35 +2182,37 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.2349869407023022</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.02570888471275136</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2836160659790039</v>
+        <v>0.5594650506973267</v>
       </c>
       <c r="F41" t="n">
-        <v>12.42500000000001</v>
+        <v>48.77977897252092</v>
       </c>
       <c r="G41" t="n">
-        <v>0.04869684499314129</v>
+        <v>0.5130315500685871</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
       <c r="K41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.2752293577981652</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4262295081967214</v>
       </c>
     </row>
     <row r="42">
@@ -2145,35 +2225,37 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01273885288652687</v>
+        <v>0.2447257337962222</v>
       </c>
       <c r="D42" t="n">
-        <v>7.842246496009318e-255</v>
+        <v>3.960183021215134e-79</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3234778940677643</v>
+        <v>0.5474337339401245</v>
       </c>
       <c r="F42" t="n">
-        <v>12.42500000000001</v>
+        <v>26.4907079646018</v>
       </c>
       <c r="G42" t="n">
-        <v>0.08114285714285714</v>
+        <v>0.5725714285714286</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
       <c r="K42" t="n">
         <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2391304347826087</v>
       </c>
     </row>
     <row r="43">
@@ -2186,35 +2268,37 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.2249999950195314</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>9.255580072322822e-79</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3453939259052277</v>
+        <v>0.6323580741882324</v>
       </c>
       <c r="F43" t="n">
-        <v>12.42500000000001</v>
+        <v>48.31562598770853</v>
       </c>
       <c r="G43" t="n">
-        <v>0.06580166821130677</v>
+        <v>1.009267840593142</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="M43" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4146341463414633</v>
       </c>
     </row>
     <row r="44">
@@ -2227,35 +2311,37 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.2575107254802999</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>6.074225558490695e-79</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3232988715171814</v>
+        <v>0.5784918069839478</v>
       </c>
       <c r="F44" t="n">
-        <v>12.42500000000001</v>
+        <v>63.88143805309736</v>
       </c>
       <c r="G44" t="n">
-        <v>0.08151549942594719</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>0.4035087719298245</v>
       </c>
       <c r="M44" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2929292929292929</v>
       </c>
     </row>
     <row r="45">
@@ -2268,35 +2354,37 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.2475355920125149</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>0.03272991541674167</v>
       </c>
       <c r="E45" t="n">
-        <v>0.3477978110313416</v>
+        <v>0.6097379922866821</v>
       </c>
       <c r="F45" t="n">
-        <v>12.42500000000001</v>
+        <v>28.86907136420979</v>
       </c>
       <c r="G45" t="n">
-        <v>0.01946805593638607</v>
+        <v>0.8050452426652043</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>0.2112676056338028</v>
       </c>
       <c r="M45" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.7108433734939759</v>
       </c>
     </row>
     <row r="46">
@@ -2309,35 +2397,37 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.2015503849983054</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>0.001454827592964839</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3389484584331512</v>
+        <v>0.6179981231689453</v>
       </c>
       <c r="F46" t="n">
-        <v>12.42500000000001</v>
+        <v>56.16400000000002</v>
       </c>
       <c r="G46" t="n">
-        <v>0.01966214345056771</v>
+        <v>0.1827748546109111</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
       <c r="K46" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>0.2413793103448276</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3396226415094339</v>
       </c>
     </row>
     <row r="47">
@@ -2350,35 +2440,37 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.3024910988109953</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.01061049447037906</v>
       </c>
       <c r="E47" t="n">
-        <v>0.355352520942688</v>
+        <v>0.6742040514945984</v>
       </c>
       <c r="F47" t="n">
-        <v>12.42500000000001</v>
+        <v>31.17213675213677</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0282981267437226</v>
+        <v>0.5041849342367477</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
       <c r="K47" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>0.2797202797202797</v>
       </c>
       <c r="M47" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.4240837696335079</v>
       </c>
     </row>
     <row r="48">
@@ -2391,35 +2483,37 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.2095238055256237</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>5.133701126708558e-156</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3648593723773956</v>
+        <v>0.5640274286270142</v>
       </c>
       <c r="F48" t="n">
-        <v>12.42500000000001</v>
+        <v>34.85500000000002</v>
       </c>
       <c r="G48" t="n">
-        <v>0.15203426124197</v>
+        <v>0.4753747323340471</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
       <c r="K48" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="M48" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.09090909090909091</v>
       </c>
     </row>
     <row r="49">
@@ -2432,35 +2526,37 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1518987292421088</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>6.976978506231785e-79</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3483927845954895</v>
+        <v>0.5996517539024353</v>
       </c>
       <c r="F49" t="n">
-        <v>12.42500000000001</v>
+        <v>42.1806666666667</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1368015414258189</v>
+        <v>0.9807321772639692</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
       <c r="K49" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="M49" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2682926829268293</v>
       </c>
     </row>
     <row r="50">
@@ -2473,35 +2569,37 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.1437125698648214</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>2.541527550043149e-155</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3485001027584076</v>
+        <v>0.5909938812255859</v>
       </c>
       <c r="F50" t="n">
-        <v>12.42500000000001</v>
+        <v>35.70261904761907</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1360153256704981</v>
+        <v>1.044061302681992</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
       <c r="K50" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="M50" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.2737430167597765</v>
       </c>
     </row>
     <row r="51">
@@ -2514,35 +2612,37 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.2916666617730035</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>0.04707568738114142</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3496768474578857</v>
+        <v>0.6445941925048828</v>
       </c>
       <c r="F51" t="n">
-        <v>12.42500000000001</v>
+        <v>47.56272515527951</v>
       </c>
       <c r="G51" t="n">
-        <v>0.09454061251664447</v>
+        <v>1.360852197070572</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
       <c r="K51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="M51" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.4954128440366973</v>
       </c>
     </row>
     <row r="52">
@@ -2555,35 +2655,37 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.008403360933196829</v>
+        <v>0.1296758056051892</v>
       </c>
       <c r="D52" t="n">
-        <v>2.960553565183628e-265</v>
+        <v>3.111804530170546e-155</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3448955118656158</v>
+        <v>0.5799024701118469</v>
       </c>
       <c r="F52" t="n">
-        <v>12.42500000000001</v>
+        <v>31.39079634113534</v>
       </c>
       <c r="G52" t="n">
-        <v>0.05148658448150834</v>
+        <v>0.8375634517766497</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>0.1592920353982301</v>
       </c>
       <c r="M52" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.5336787564766839</v>
       </c>
     </row>
     <row r="53">
@@ -2596,35 +2698,37 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.2978723355045663</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>0.05028871028667643</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3169403970241547</v>
+        <v>0.6696712970733643</v>
       </c>
       <c r="F53" t="n">
-        <v>12.42500000000001</v>
+        <v>13.99549059929498</v>
       </c>
       <c r="G53" t="n">
-        <v>0.03788687299893276</v>
+        <v>0.8303094983991463</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>0.2674418604651163</v>
       </c>
       <c r="M53" t="n">
-        <v>0.04761904761904762</v>
+        <v>0.539877300613497</v>
       </c>
     </row>
     <row r="54">
@@ -2637,35 +2741,37 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.2796833723563607</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>0.0775308455254218</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3199907243251801</v>
+        <v>0.6482086181640625</v>
       </c>
       <c r="F54" t="n">
-        <v>12.42500000000001</v>
+        <v>24.74805048198886</v>
       </c>
       <c r="G54" t="n">
-        <v>0.05224429727740986</v>
+        <v>0.8447387785136129</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
       <c r="K54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>0.2846715328467153</v>
       </c>
       <c r="M54" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.393939393939394</v>
       </c>
     </row>
     <row r="55">
@@ -2678,35 +2784,37 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.2145110371742181</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>0.01531087589563896</v>
       </c>
       <c r="E55" t="n">
-        <v>0.3372025191783905</v>
+        <v>0.6238362193107605</v>
       </c>
       <c r="F55" t="n">
-        <v>12.42500000000001</v>
+        <v>39.9100174825175</v>
       </c>
       <c r="G55" t="n">
-        <v>0.04592496765847348</v>
+        <v>0.3479948253557568</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.1052631578947368</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
       <c r="K55" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>0.3283582089552239</v>
       </c>
       <c r="M55" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.3023255813953488</v>
       </c>
     </row>
     <row r="56">
@@ -2741,7 +2849,7 @@
       </c>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -2823,7 +2931,7 @@
       </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -2864,7 +2972,7 @@
       </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -2905,7 +3013,7 @@
       </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -2946,7 +3054,7 @@
       </c>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -2987,7 +3095,7 @@
       </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -3028,7 +3136,7 @@
       </c>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -3069,7 +3177,7 @@
       </c>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -3110,7 +3218,7 @@
       </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -3151,7 +3259,7 @@
       </c>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -3233,7 +3341,7 @@
       </c>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
